--- a/astro-site/public/dl/kit-tareas-hamburgueseria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/05-tareas-semanales-mensuales.xlsx
@@ -222,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -310,6 +310,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -791,6 +797,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="23" t="inlineStr">
         <is>
@@ -798,6 +805,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="32" customHeight="1">
       <c r="B24" s="24" t="inlineStr">
         <is>
@@ -812,6 +820,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="23" t="inlineStr">
         <is>
@@ -819,6 +828,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="16" customHeight="1">
       <c r="B29" s="24" t="inlineStr">
         <is>
@@ -854,6 +864,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="23" t="inlineStr">
         <is>
@@ -861,6 +872,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37" ht="35" customHeight="1">
       <c r="B37" s="23" t="inlineStr">
         <is>
@@ -875,6 +887,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="23" t="inlineStr">
         <is>
@@ -980,10 +993,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D6" s="9" t="n">
+        <v>40</v>
       </c>
       <c r="E6" s="10">
         <f>IF(B6="","",IF(B6&lt;D6,"⚠️ PEDIR","OK"))</f>
@@ -1003,10 +1014,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="D7" s="13" t="n">
+        <v>50</v>
       </c>
       <c r="E7" s="14">
         <f>IF(B7="","",IF(B7&lt;D7,"⚠️ PEDIR","OK"))</f>
@@ -1026,10 +1035,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D8" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="E8" s="10">
         <f>IF(B8="","",IF(B8&lt;D8,"⚠️ PEDIR","OK"))</f>
@@ -1049,10 +1056,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="D9" s="13" t="n">
+        <v>20</v>
       </c>
       <c r="E9" s="14">
         <f>IF(B9="","",IF(B9&lt;D9,"⚠️ PEDIR","OK"))</f>
@@ -1079,10 +1084,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D11" s="13" t="n">
+        <v>40</v>
       </c>
       <c r="E11" s="14">
         <f>IF(B11="","",IF(B11&lt;D11,"⚠️ PEDIR","OK"))</f>
@@ -1102,10 +1105,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="D12" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="E12" s="10">
         <f>IF(B12="","",IF(B12&lt;D12,"⚠️ PEDIR","OK"))</f>
@@ -1125,10 +1126,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="D13" s="13" t="n">
+        <v>20</v>
       </c>
       <c r="E13" s="14">
         <f>IF(B13="","",IF(B13&lt;D13,"⚠️ PEDIR","OK"))</f>
@@ -1155,10 +1154,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="D15" s="13" t="n">
+        <v>50</v>
       </c>
       <c r="E15" s="14">
         <f>IF(B15="","",IF(B15&lt;D15,"⚠️ PEDIR","OK"))</f>
@@ -1178,10 +1175,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="D16" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="E16" s="10">
         <f>IF(B16="","",IF(B16&lt;D16,"⚠️ PEDIR","OK"))</f>
@@ -1201,10 +1196,8 @@
           <t>g</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="D17" s="13" t="n">
+        <v>300</v>
       </c>
       <c r="E17" s="14">
         <f>IF(B17="","",IF(B17&lt;D17,"⚠️ PEDIR","OK"))</f>
@@ -1224,10 +1217,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="D18" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="E18" s="10">
         <f>IF(B18="","",IF(B18&lt;D18,"⚠️ PEDIR","OK"))</f>
@@ -1254,10 +1245,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D20" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="E20" s="10">
         <f>IF(B20="","",IF(B20&lt;D20,"⚠️ PEDIR","OK"))</f>
@@ -1277,10 +1266,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D21" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="E21" s="14">
         <f>IF(B21="","",IF(B21&lt;D21,"⚠️ PEDIR","OK"))</f>
@@ -1300,10 +1287,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D22" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="E22" s="10">
         <f>IF(B22="","",IF(B22&lt;D22,"⚠️ PEDIR","OK"))</f>
@@ -1323,10 +1308,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D23" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="E23" s="14">
         <f>IF(B23="","",IF(B23&lt;D23,"⚠️ PEDIR","OK"))</f>
@@ -1346,10 +1329,8 @@
           <t>g</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="D24" s="9" t="n">
+        <v>300</v>
       </c>
       <c r="E24" s="10">
         <f>IF(B24="","",IF(B24&lt;D24,"⚠️ PEDIR","OK"))</f>
@@ -1369,10 +1350,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D25" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="E25" s="14">
         <f>IF(B25="","",IF(B25&lt;D25,"⚠️ PEDIR","OK"))</f>
@@ -1392,10 +1371,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D26" s="9" t="n">
+        <v>0.5</v>
       </c>
       <c r="E26" s="10">
         <f>IF(B26="","",IF(B26&lt;D26,"⚠️ PEDIR","OK"))</f>
@@ -1415,10 +1392,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D27" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="E27" s="14">
         <f>IF(B27="","",IF(B27&lt;D27,"⚠️ PEDIR","OK"))</f>
@@ -1438,10 +1413,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D28" s="9" t="n">
+        <v>0.5</v>
       </c>
       <c r="E28" s="10">
         <f>IF(B28="","",IF(B28&lt;D28,"⚠️ PEDIR","OK"))</f>
@@ -1468,10 +1441,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="D30" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="E30" s="10">
         <f>IF(B30="","",IF(B30&lt;D30,"⚠️ PEDIR","OK"))</f>
@@ -1491,10 +1462,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D31" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="E31" s="14">
         <f>IF(B31="","",IF(B31&lt;D31,"⚠️ PEDIR","OK"))</f>
@@ -1514,10 +1483,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="D32" s="9" t="n">
+        <v>30</v>
       </c>
       <c r="E32" s="10">
         <f>IF(B32="","",IF(B32&lt;D32,"⚠️ PEDIR","OK"))</f>
@@ -1537,10 +1504,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D33" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="E33" s="14">
         <f>IF(B33="","",IF(B33&lt;D33,"⚠️ PEDIR","OK"))</f>
@@ -1567,10 +1532,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D35" s="13" t="n">
+        <v>40</v>
       </c>
       <c r="E35" s="14">
         <f>IF(B35="","",IF(B35&lt;D35,"⚠️ PEDIR","OK"))</f>
@@ -1590,10 +1553,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D36" s="9" t="n">
+        <v>40</v>
       </c>
       <c r="E36" s="10">
         <f>IF(B36="","",IF(B36&lt;D36,"⚠️ PEDIR","OK"))</f>
@@ -1613,10 +1574,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="D37" s="13" t="n">
+        <v>30</v>
       </c>
       <c r="E37" s="14">
         <f>IF(B37="","",IF(B37&lt;D37,"⚠️ PEDIR","OK"))</f>
@@ -1636,10 +1595,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="D38" s="9" t="n">
+        <v>100</v>
       </c>
       <c r="E38" s="10">
         <f>IF(B38="","",IF(B38&lt;D38,"⚠️ PEDIR","OK"))</f>
@@ -1647,6 +1604,7 @@
       </c>
       <c r="F38" s="8" t="n"/>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -1657,14 +1615,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A10:F10"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2046,7 +2004,7 @@
       </c>
       <c r="D21" s="19">
         <f>COUNTIFS(B5:B19,"?*",F5:F19,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
@@ -2055,7 +2013,7 @@
       </c>
       <c r="F21">
         <f>COUNTIF(B5:B19,"?*")-COUNTIF(F5:F19,"N/A")</f>
-        <v>8.0</v>
+        <v/>
       </c>
     </row>
     <row r="22"/>
@@ -2079,11 +2037,11 @@
   <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G19">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -2502,7 +2460,7 @@
       </c>
       <c r="D22" s="19">
         <f>COUNTIFS(B5:B20,"?*",F5:F20,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
@@ -2511,7 +2469,7 @@
       </c>
       <c r="F22">
         <f>COUNTIF(B5:B20,"?*")-COUNTIF(F5:F20,"N/A")</f>
-        <v>9.0</v>
+        <v/>
       </c>
     </row>
     <row r="23"/>
@@ -2568,9 +2526,9 @@
           <t>Congélalos ya porcionados y separados con papel: la picada tiene mucha superficie expuesta y se enrancia antes que la pieza entera</t>
         </is>
       </c>
-      <c r="E28" s="35" t="n"/>
-      <c r="F28" s="35" t="n"/>
-      <c r="G28" s="36" t="n"/>
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="37" t="n"/>
+      <c r="G28" s="38" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="20" t="n"/>
@@ -2589,9 +2547,9 @@
           <t>La grasa se enrancia aunque esté congelada: es lo primero que sabe a viejo</t>
         </is>
       </c>
-      <c r="E29" s="35" t="n"/>
-      <c r="F29" s="35" t="n"/>
-      <c r="G29" s="36" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="38" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="20" t="n"/>
@@ -2610,9 +2568,9 @@
           <t>Del congelador a la freidora, sin descongelar: si se atempera suelta agua y el rebozado se despega</t>
         </is>
       </c>
-      <c r="E30" s="35" t="n"/>
-      <c r="F30" s="35" t="n"/>
-      <c r="G30" s="36" t="n"/>
+      <c r="E30" s="37" t="n"/>
+      <c r="F30" s="37" t="n"/>
+      <c r="G30" s="38" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="20" t="n"/>
@@ -2631,9 +2589,9 @@
           <t>Congélalo el día que llega, no cuando ya se está pasando; descongela a temperatura ambiente dentro de su bolsa</t>
         </is>
       </c>
-      <c r="E31" s="35" t="n"/>
-      <c r="F31" s="35" t="n"/>
-      <c r="G31" s="36" t="n"/>
+      <c r="E31" s="37" t="n"/>
+      <c r="F31" s="37" t="n"/>
+      <c r="G31" s="38" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="20" t="n"/>
@@ -2652,9 +2610,9 @@
           <t>NUNCA se descongelan: van del congelador al aceite o quedan blandas y salpican</t>
         </is>
       </c>
-      <c r="E32" s="35" t="n"/>
-      <c r="F32" s="35" t="n"/>
-      <c r="G32" s="36" t="n"/>
+      <c r="E32" s="37" t="n"/>
+      <c r="F32" s="37" t="n"/>
+      <c r="G32" s="38" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="20" t="n"/>
@@ -2673,9 +2631,9 @@
           <t>Igual que las patatas: directos al aceite</t>
         </is>
       </c>
-      <c r="E33" s="35" t="n"/>
-      <c r="F33" s="35" t="n"/>
-      <c r="G33" s="36" t="n"/>
+      <c r="E33" s="37" t="n"/>
+      <c r="F33" s="37" t="n"/>
+      <c r="G33" s="38" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="20" t="n"/>
@@ -2694,9 +2652,9 @@
           <t>Se vuelve quebradizo al descongelar pero funde igual: úsalo sólo para fundir, no en frío</t>
         </is>
       </c>
-      <c r="E34" s="35" t="n"/>
-      <c r="F34" s="35" t="n"/>
-      <c r="G34" s="36" t="n"/>
+      <c r="E34" s="37" t="n"/>
+      <c r="F34" s="37" t="n"/>
+      <c r="G34" s="38" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="20" t="n"/>
@@ -2715,9 +2673,9 @@
           <t>Etiquetar con fecha de producción Y de congelación: la vida útil de esta tabla se cuenta desde la de congelación</t>
         </is>
       </c>
-      <c r="E35" s="35" t="n"/>
-      <c r="F35" s="35" t="n"/>
-      <c r="G35" s="36" t="n"/>
+      <c r="E35" s="37" t="n"/>
+      <c r="F35" s="37" t="n"/>
+      <c r="G35" s="38" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="20" t="n"/>
@@ -2736,9 +2694,9 @@
           <t>Sin escaldar previamente, la mitad</t>
         </is>
       </c>
-      <c r="E36" s="35" t="n"/>
-      <c r="F36" s="35" t="n"/>
-      <c r="G36" s="36" t="n"/>
+      <c r="E36" s="37" t="n"/>
+      <c r="F36" s="37" t="n"/>
+      <c r="G36" s="38" t="n"/>
     </row>
     <row r="37"/>
     <row r="38">
@@ -2751,24 +2709,24 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="18">
-    <mergeCell ref="A12:G12"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D30:G30"/>
     <mergeCell ref="D34:G34"/>
     <mergeCell ref="D29:G29"/>
     <mergeCell ref="D27:G27"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D28:G28"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A24:G24"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G20">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -3160,7 +3118,7 @@
       </c>
       <c r="D21" s="19">
         <f>COUNTIFS(B5:B19,"?*",F5:F19,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
@@ -3169,7 +3127,7 @@
       </c>
       <c r="F21">
         <f>COUNTIF(B5:B19,"?*")-COUNTIF(F5:F19,"N/A")</f>
-        <v>8.0</v>
+        <v/>
       </c>
     </row>
     <row r="22"/>
@@ -3193,11 +3151,11 @@
   <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G19">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -3708,7 +3666,7 @@
       </c>
       <c r="D28" s="19">
         <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
@@ -3717,7 +3675,7 @@
       </c>
       <c r="F28">
         <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
-        <v>14.0</v>
+        <v/>
       </c>
     </row>
     <row r="29"/>
@@ -3739,14 +3697,14 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
-    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A28:C28"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G26">
     <cfRule type="expression" priority="1" dxfId="0">

--- a/astro-site/public/dl/kit-tareas-hamburgueseria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/05-tareas-semanales-mensuales.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="D21" s="19">
         <f>COUNTIFS(B5:B19,"?*",F5:F19,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F21">
         <f>COUNTIF(B5:B19,"?*")-COUNTIF(F5:F19,"N/A")</f>
-        <v/>
+        <v>8.0</v>
       </c>
     </row>
     <row r="22"/>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D22" s="19">
         <f>COUNTIFS(B5:B20,"?*",F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="F22">
         <f>COUNTIF(B5:B20,"?*")-COUNTIF(F5:F20,"N/A")</f>
-        <v/>
+        <v>9.0</v>
       </c>
     </row>
     <row r="23"/>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D21" s="19">
         <f>COUNTIFS(B5:B19,"?*",F5:F19,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F21">
         <f>COUNTIF(B5:B19,"?*")-COUNTIF(F5:F19,"N/A")</f>
-        <v/>
+        <v>8.0</v>
       </c>
     </row>
     <row r="22"/>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="D28" s="19">
         <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="F28">
         <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
-        <v/>
+        <v>14.0</v>
       </c>
     </row>
     <row r="29"/>
